--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R54dab64af5894325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4078b0c66acd4a06"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,7 +346,7 @@
         <x:v>输入来源</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>虚构并脱敏的联盟结算演练数据库与业务规则</x:v>
+        <x:v>本次联盟佣金结算批次，包括字段已脱敏的订单、点击触点、合作方账户、退款记录和结算规则</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
@@ -445,12 +445,36 @@
         <x:v>orders、click_touchpoints、partner_accounts和refunds保持不变</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="33" customHeight="1">
+    <x:row r="18" ht="48" customHeight="1">
       <x:c r="A18" s="5" t="str">
+        <x:v>实现边界</x:v>
+      </x:c>
+      <x:c r="B18" s="5" t="str">
+        <x:v>数据库和规则保持只读，不连接联盟平台或外部数据库，完成版SQL、修复库和三张报表只写入output目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="33" customHeight="1">
+      <x:c r="A19" s="5" t="str">
         <x:v>完成条件</x:v>
       </x:c>
-      <x:c r="B18" s="5" t="str">
+      <x:c r="B19" s="5" t="str">
         <x:v>Python入口返回0，数据库、SQL和三张CSV可读，派生表与报表按业务主键一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="33" customHeight="1">
+      <x:c r="A20" s="5" t="str">
+        <x:v>可验证点</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="str">
+        <x:v>源表完整性、排除原因、唯一归因、退款净额、档位佣金、未归因分组和三张报表均有对应数据库记录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="33" customHeight="1">
+      <x:c r="A21" s="5" t="str">
+        <x:v>不适合作为评分点的内容</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="str">
+        <x:v>查询别名、中间对象名称、SQL缩进、关键字大小写、CSV必要引号以及LF或CRLF行尾</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/artifacts/任务规格转化.xlsx
+++ b/artifacts/任务规格转化.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R4078b0c66acd4a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务规格转化" sheetId="1" r:id="R0dd50f6d604c4604"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -351,23 +351,23 @@
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>输入获取方式</x:v>
+        <x:v>业务输入</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>解压输入数据包后在input_data目录读取database、rules、starter和tools</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="48" customHeight="1">
+        <x:v>database/affiliate_payout.db；rules/commission_rules.json；starter/rebuild_affiliate_payout.sql</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="33" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>原始输入文件</x:v>
+        <x:v>结算目标</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>database/affiliate_payout.db；rules/commission_rules.json；starter/rebuild_affiliate_payout.sql</x:v>
+        <x:v>排除不合格触点，确定每笔可付款订单的唯一归因，计算退款后净额与档位佣金，并形成合作方汇总</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="78" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>目标输出文件</x:v>
+        <x:v>交付文件</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
         <x:v>output/affiliate_payout_repaired.db；output/sql/rebuild_affiliate_payout.sql；output/reports/commission_ledger.csv；output/reports/excluded_touchpoints.csv；output/reports/partner_summary.csv</x:v>
@@ -375,106 +375,106 @@
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>核心操作链</x:v>
+        <x:v>SQLite步骤</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
         <x:v>读取结算规则；关联订单与触点；裁决排除原因；选择最后合格点击；汇总退款；计算整数分佣金；汇总合作方；导出报表</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="33" customHeight="1">
+    <x:row r="10" ht="48" customHeight="1">
       <x:c r="A10" s="5" t="str">
+        <x:v>运行入口</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="str">
+        <x:v>在input_data目录运行py tools/run_task.py，由入口复制业务库、载入结算规则、执行完成版SQL并导出报表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="33" customHeight="1">
+      <x:c r="A11" s="5" t="str">
         <x:v>触点候选</x:v>
       </x:c>
-      <x:c r="B10" s="5" t="str">
+      <x:c r="B11" s="5" t="str">
         <x:v>只关联同一user_id且click_ts不晚于order_ts的点击</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="5" t="str">
-        <x:v>排除裁决</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>依据exclusion_precedence处理订单状态、域名、窗口、自引流、欺诈分数和合作方状态</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="48" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>归因取舍</x:v>
+        <x:v>排除裁决</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>对合格候选按tie_breaker选择一条，未入选候选写入superseded_by_later_click</x:v>
+        <x:v>依据exclusion_precedence处理订单状态、域名、窗口、自引流、欺诈分数和合作方状态</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="48" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>订单净额</x:v>
+        <x:v>归因取舍</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>net_amount_cents等于order_amount_cents减去该订单全部refund_amount_cents</x:v>
+        <x:v>对合格候选按tie_breaker选择一条，未入选候选写入superseded_by_later_click</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="48" customHeight="1">
       <x:c r="A14" s="5" t="str">
+        <x:v>订单净额</x:v>
+      </x:c>
+      <x:c r="B14" s="5" t="str">
+        <x:v>net_amount_cents等于order_amount_cents减去该订单全部refund_amount_cents</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="5" t="str">
         <x:v>佣金计算</x:v>
       </x:c>
-      <x:c r="B14" s="5" t="str">
+      <x:c r="B15" s="5" t="str">
         <x:v>按partner_accounts.tier映射commission_rate_bps_by_tier，并依commission_rounding计算整数分</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="33" customHeight="1">
-      <x:c r="A15" s="5" t="str">
+    <x:row r="16" ht="33" customHeight="1">
+      <x:c r="A16" s="5" t="str">
         <x:v>未归因订单</x:v>
       </x:c>
-      <x:c r="B15" s="5" t="str">
+      <x:c r="B16" s="5" t="str">
         <x:v>所有可付款订单进入commission_ledger，无合格触点时归因字段为空且佣金为0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="48" customHeight="1">
-      <x:c r="A16" s="5" t="str">
-        <x:v>合作方汇总</x:v>
-      </x:c>
-      <x:c r="B16" s="5" t="str">
-        <x:v>按partner_id汇总订单数、净额、佣金和有序order_ids，空partner_id归入UNATTRIBUTED</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="48" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>输入保护</x:v>
+        <x:v>合作方汇总</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>orders、click_touchpoints、partner_accounts和refunds保持不变</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="48" customHeight="1">
+        <x:v>按partner_id汇总订单数、净额、佣金和有序order_ids，空partner_id归入UNATTRIBUTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="63" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>实现边界</x:v>
+        <x:v>业务材料边界</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>数据库和规则保持只读，不连接联盟平台或外部数据库，完成版SQL、修复库和三张报表只写入output目录</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="33" customHeight="1">
+        <x:v>orders、click_touchpoints、partner_accounts、refunds和commission_rules.json保持只读，完成版SQL、修复库和三张报表写入output目录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>完成条件</x:v>
+        <x:v>财务交接</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>Python入口返回0，数据库、SQL和三张CSV可读，派生表与报表按业务主键一致</x:v>
+        <x:v>commission_ledger用于生成付款明细，partner_summary用于核对合作方结算，excluded_touchpoints供风控追查排除原因</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="33" customHeight="1">
       <x:c r="A20" s="5" t="str">
-        <x:v>可验证点</x:v>
+        <x:v>结果对账</x:v>
       </x:c>
       <x:c r="B20" s="5" t="str">
-        <x:v>源表完整性、排除原因、唯一归因、退款净额、档位佣金、未归因分组和三张报表均有对应数据库记录</x:v>
+        <x:v>排除原因、唯一归因、退款净额、档位佣金和未归因分组均能从业务材料、派生表与三张报表相互核对</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="33" customHeight="1">
       <x:c r="A21" s="5" t="str">
-        <x:v>不适合作为评分点的内容</x:v>
+        <x:v>实现边界</x:v>
       </x:c>
       <x:c r="B21" s="5" t="str">
-        <x:v>查询别名、中间对象名称、SQL缩进、关键字大小写、CSV必要引号以及LF或CRLF行尾</x:v>
+        <x:v>查询别名、中间对象名称和SQL组织可以不同，源表只读、派生表结构、业务结果与报表排序保持一致</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
